--- a/design/00-总览与状态/数值真值表.xlsx
+++ b/design/00-总览与状态/数值真值表.xlsx
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>16 档：20~160；基准路线练气 30</t>
+          <t>5 阶：20~140；基准路线练气 20</t>
         </is>
       </c>
     </row>
@@ -867,14 +867,14 @@
         <v>100</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.16064</v>
+        <v>0.77376</v>
       </c>
       <c r="E18" s="13">
         <f>C18*D18*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0.08</v>
@@ -931,14 +931,14 @@
         <v>150</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2.042726</v>
+        <v>1.361818</v>
       </c>
       <c r="E19" s="13">
         <f>C19*D19*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F19" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0.08</v>
@@ -996,14 +996,14 @@
         <v>300</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1.949336</v>
+        <v>1.299557</v>
       </c>
       <c r="E20" s="13">
         <f>C20*D20*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>0.16</v>
@@ -1061,14 +1061,14 @@
         <v>450</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.078078</v>
+        <v>1.385385</v>
       </c>
       <c r="E21" s="13">
         <f>C21*D21*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.16</v>
@@ -1126,14 +1126,14 @@
         <v>700</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.136204</v>
+        <v>1.424136</v>
       </c>
       <c r="E22" s="13">
         <f>C22*D22*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F22" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>0.16</v>
@@ -1191,14 +1191,14 @@
         <v>1300</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1.900548</v>
+        <v>1.267032</v>
       </c>
       <c r="E23" s="13">
         <f>C23*D23*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F23" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0.27</v>
@@ -1256,14 +1256,14 @@
         <v>2000</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.669001</v>
+        <v>1.112668</v>
       </c>
       <c r="E24" s="13">
         <f>C24*D24*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F24" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>0.27</v>
@@ -1321,14 +1321,14 @@
         <v>3000</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.503246</v>
+        <v>1.002164</v>
       </c>
       <c r="E25" s="13">
         <f>C25*D25*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F25" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.27</v>
@@ -1386,14 +1386,14 @@
         <v>5600</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1.466692</v>
+        <v>0.977795</v>
       </c>
       <c r="E26" s="13">
         <f>C26*D26*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F26" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>0.48</v>
@@ -1451,14 +1451,14 @@
         <v>8500</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1.530606</v>
+        <v>1.020404</v>
       </c>
       <c r="E27" s="13">
         <f>C27*D27*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F27" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0.48</v>
@@ -1516,14 +1516,14 @@
         <v>18000</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2.217962</v>
+        <v>1.848301</v>
       </c>
       <c r="E28" s="13">
         <f>C28*D28*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F28" s="9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>0.5600000000000001</v>
@@ -1581,14 +1581,14 @@
         <v>27000</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.065533</v>
+        <v>1.721277</v>
       </c>
       <c r="E29" s="13">
         <f>C29*D29*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F29" s="9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0.5600000000000001</v>
@@ -1646,14 +1646,14 @@
         <v>40000</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1.947624</v>
+        <v>1.62302</v>
       </c>
       <c r="E30" s="13">
         <f>C30*D30*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F30" s="9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>0.5600000000000001</v>
@@ -1711,14 +1711,14 @@
         <v>60000</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.285213</v>
+        <v>1.904344</v>
       </c>
       <c r="E31" s="13">
         <f>C31*D31*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F31" s="9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>0.5600000000000001</v>
@@ -1776,14 +1776,14 @@
         <v>120000</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3.066285</v>
+        <v>2.453028</v>
       </c>
       <c r="E32" s="13">
         <f>C32*D32*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F32" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0.8</v>
@@ -1841,14 +1841,14 @@
         <v>160000</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.91875</v>
+        <v>2.335</v>
       </c>
       <c r="E33" s="13">
         <f>C33*D33*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F33" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>0.8</v>
@@ -1906,14 +1906,14 @@
         <v>200000</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.963535</v>
+        <v>2.370828</v>
       </c>
       <c r="E34" s="13">
         <f>C34*D34*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F34" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>0.8</v>
@@ -1971,14 +1971,14 @@
         <v>240000</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.963535</v>
+        <v>2.370828</v>
       </c>
       <c r="E35" s="13">
         <f>C35*D35*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F35" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0.8</v>
@@ -2034,14 +2034,14 @@
         <v>360000</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2.963535</v>
+        <v>2.370828</v>
       </c>
       <c r="E36" s="13">
         <f>C36*D36*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F36" s="9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
@@ -2097,14 +2097,14 @@
         <v>540000</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.963535</v>
+        <v>2.370828</v>
       </c>
       <c r="E37" s="13">
         <f>C37*D37*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F37" s="9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
@@ -2160,14 +2160,14 @@
         <v>810000</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.963535</v>
+        <v>2.370828</v>
       </c>
       <c r="E38" s="13">
         <f>C38*D38*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F38" s="9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
@@ -2223,14 +2223,14 @@
         <v>1215000</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.963535</v>
+        <v>2.370828</v>
       </c>
       <c r="E39" s="13">
         <f>C39*D39*(1+$B$9)</f>
         <v/>
       </c>
       <c r="F39" s="9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
@@ -2802,11 +2802,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>与 Sheet 1 同口径</t>
+          <t>与 Sheet 1 同口径（5 阶 20~140）</t>
         </is>
       </c>
     </row>
@@ -3480,8 +3480,8 @@
   <mergeCells count="18">
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="C7:J7"/>
     <mergeCell ref="C29:J29"/>
-    <mergeCell ref="C7:J7"/>
     <mergeCell ref="A21:Q21"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="A34:Q34"/>
